--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\posicoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2056C-DAA9-42EE-9D6F-5069AA12E9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E74B5BE-F668-4B69-A8F7-F0FCB202C3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28860" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="222">
   <si>
     <t>GRUPO GERAL</t>
   </si>
@@ -697,6 +697,12 @@
   </si>
   <si>
     <t>Rosimeire Faustino Da Silva Kusomoto - CS</t>
+  </si>
+  <si>
+    <t>CANAA AGRONEGOCIOS LTDA</t>
+  </si>
+  <si>
+    <t>CANAA AGRONEGOCIOS LTDA - BTG</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DB8E20E-57E2-4347-94BA-5457C4460B8B}">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.140625" bestFit="1" customWidth="1"/>
@@ -4130,6 +4136,35 @@
         <v>198</v>
       </c>
     </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" s="4">
+        <v>23572514</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\posicoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E74B5BE-F668-4B69-A8F7-F0FCB202C3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2D70F9-2205-4B32-97EC-A055C03A5107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\posicoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2D70F9-2205-4B32-97EC-A055C03A5107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5AD16B-2E7C-4A2D-97B0-D9A8742A8696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="239">
   <si>
     <t>GRUPO GERAL</t>
   </si>
@@ -703,6 +703,57 @@
   </si>
   <si>
     <t>CANAA AGRONEGOCIOS LTDA - BTG</t>
+  </si>
+  <si>
+    <t>LELIS EMPREENDIMENTOS E LOTEAMENTOS IMOBILIARIOS LTDA</t>
+  </si>
+  <si>
+    <t>LELIS EMPREENDIMENTOS E LOTEAMENTOS IMOBILIARIOS LTDA - BTG</t>
+  </si>
+  <si>
+    <t>RVS PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>RVS PARTICIPACOES LTDA - BTG</t>
+  </si>
+  <si>
+    <t>DANIELLE SOLETTI SARTORI BISSONI</t>
+  </si>
+  <si>
+    <t>DANIELLE SOLETTI SARTORI BISSONI - XP</t>
+  </si>
+  <si>
+    <t>BRITO GESTAO E COORDENACAO DE CLINICAS LTDA</t>
+  </si>
+  <si>
+    <t>BRITO GESTAO E COORDENACAO DE CLINICAS LTDA -  XP</t>
+  </si>
+  <si>
+    <t>MONICA WENDT</t>
+  </si>
+  <si>
+    <t>MONICA WENDT - XP</t>
+  </si>
+  <si>
+    <t>IOLIVAN JOSE DE BRITO &amp;</t>
+  </si>
+  <si>
+    <t>IOLIVAN JOSE DE BRITO &amp; - CS</t>
+  </si>
+  <si>
+    <t>DREAMERS BRA LLC</t>
+  </si>
+  <si>
+    <t>DREAMERS BRA LLC - CS</t>
+  </si>
+  <si>
+    <t>RACHELE FERREIRA ROSMO - CS</t>
+  </si>
+  <si>
+    <t>M2wm</t>
+  </si>
+  <si>
+    <t>M WEALTH - BTG</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DB8E20E-57E2-4347-94BA-5457C4460B8B}">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.140625" bestFit="1" customWidth="1"/>
@@ -4165,6 +4216,267 @@
         <v>218</v>
       </c>
     </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E107" s="4">
+        <v>21272927</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E108" s="4">
+        <v>9248969</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="4">
+        <v>19003827</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="4">
+        <v>19301650</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" s="4">
+        <v>19515384</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" s="4">
+        <v>23638180</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" s="4">
+        <v>63338577</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E114" s="4">
+        <v>61160053</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E115" s="4">
+        <v>5949720</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/posicoes/Contas.xlsx
+++ b/posicoes/Contas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 11\Downloads\Aplicativo Alocação\posicoes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5AD16B-2E7C-4A2D-97B0-D9A8742A8696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8797B2-1E2E-4190-8EDC-0F18F2E7B0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{47FFE36B-B55E-4072-B31D-F6BDDA59CBE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$106</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4189,7 +4180,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>206</v>
